--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_arica_y_parinacota.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:11</t>
+    <t xml:space="preserve">2026-09-09 22:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_arica_y_parinacota.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:08</t>
+    <t xml:space="preserve">2026-09-17 13:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_arica_y_parinacota.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:39</t>
+    <t xml:space="preserve">2026-09-25 21:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_arica_y_parinacota.xlsx
@@ -6,69 +6,50 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Barras" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Provincias" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mapa" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Serie" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sexo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Serie'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sexo'!$A$1:$D$4</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t xml:space="preserve">Provincia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subgrupo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_prev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delta_pp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delta_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prov_rank</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t xml:space="preserve">Unidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor anio anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frente a la region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frente al anio anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Región de Arica y Parinacota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica</t>
   </si>
   <si>
     <t xml:space="preserve">Parinacota</t>
   </si>
   <si>
-    <t xml:space="preserve">Femenino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masculino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promedio Regional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arica</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
-    <t xml:space="preserve">Valor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 21:34</t>
+    <t xml:space="preserve">2026-09-28 21:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -86,31 +67,25 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Mediana ingreso de asalariados dependientes</t>
+    <t xml:space="preserve">I_INGR_MEDIAN_a</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Arica y Parinacota</t>
-  </si>
-  <si>
     <t xml:space="preserve">Año</t>
   </si>
   <si>
     <t xml:space="preserve">2024</t>
   </si>
   <si>
-    <t xml:space="preserve">ano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_hist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023</t>
+    <t xml:space="preserve">Mujeres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hombres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brecha de las mujeres</t>
   </si>
 </sst>
 </file>
@@ -475,13 +450,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="21.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="25.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,222 +473,58 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>915909</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>662500</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>575000</v>
-      </c>
+        <v>838130</v>
+      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2" t="n">
-        <v>87500</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>15.22</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>3</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>917024</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>812500</v>
+        <v>839484</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>750000</v>
+        <v>0.1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>62500</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>3</v>
+        <v>9.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
+      <c r="B4" s="2" t="n">
+        <v>767934</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>767934.5</v>
+        <v>697650</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>697650</v>
+        <v>-16.2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>70284.5</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>805640</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>733970</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>71670</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>986426</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>916423</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>70003</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>915909</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>838130</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>77779</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>9.28</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>806433</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>734715</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>71718</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>988000</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>917656</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>70344</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>917024</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>839484</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>77540</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>9.24</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:E4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -732,58 +541,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -797,8 +606,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -806,154 +617,59 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>917024</v>
+        <v>805640</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>986426</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>-18.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>767934.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B3"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>736812</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>806433</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>839484</v>
+        <v>988000</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-18.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>662500</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>917024</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>617090</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>697650</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>767934.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>735910</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>838130</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>915909</v>
+        <v>812500</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-18.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10"/>
+  <autoFilter ref="A1:D4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_arica_y_parinacota.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:39</t>
+    <t xml:space="preserve">2026-10-05 07:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -511,7 +511,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>767934</v>
+        <v>767935</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>697650</v>
